--- a/business_forms/049_trade_season_pass_registration--business_forms.xlsx
+++ b/business_forms/049_trade_season_pass_registration--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
